--- a/experiments/saline_exposure_120h/sensor_corrosion_experiment_results.xlsx
+++ b/experiments/saline_exposure_120h/sensor_corrosion_experiment_results.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline Raw Data" sheetId="1" r:id="R094e1257d93e432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline Summary" sheetId="2" r:id="R50ead2fad1cb4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Observations" sheetId="3" r:id="R3e574cd084934eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Post-Exposure Raw" sheetId="4" r:id="R3e9b293bee2448ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drift Analysis" sheetId="5" r:id="R534b26660e6f429b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preliminary Checks" sheetId="6" r:id="R2e232c6dea8e4f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results Summary" sheetId="7" r:id="R5e83e6ac84504722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline Raw Data" sheetId="1" r:id="R4ba5e97edd3441ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline Summary" sheetId="2" r:id="R3529f122272d4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Observations" sheetId="3" r:id="R00c53ba4298641fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Post-Exposure Raw" sheetId="4" r:id="Rcf3d7e5810e044b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drift Analysis" sheetId="5" r:id="Rf9531fd50079435d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preliminary Checks" sheetId="6" r:id="R108a5aed588a4cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results Summary" sheetId="7" r:id="R1b471319761242f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -305,7 +305,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -488,6 +488,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -495,7 +510,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF2FA"/>
         </x:patternFill>
       </x:fill>
@@ -692,7 +707,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R032f949bfe2b4c92"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R079f05d38a774035"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2713,7 +2728,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e3d11676d48401b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b5ca6c1be674809"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3230,7 +3245,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R144beb1288e14663"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959bede0faad4d48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3241,18 +3256,18 @@
   <x:cols>
     <x:col min="1" max="1" width="41.66999816894531" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="15.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="19" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -3273,7 +3288,7 @@
       <x:c r="M1" s="95"/>
       <x:c r="N1" s="95"/>
     </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="8" t="str">
         <x:v>Day</x:v>
       </x:c>
@@ -3317,795 +3332,1059 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="28" t="n">
+    <x:row r="3" ht="32" customHeight="1">
+      <x:c r="A3" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" s="28" t="n">
+      <x:c r="B3" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C3" s="37" t="str"/>
-      <x:c r="D3" s="38" t="str"/>
-      <x:c r="E3" s="29" t="str">
+      <x:c r="C3" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D3" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E3" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F3" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G3" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H3" s="39" t="str">
+      <x:c r="F3" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G3" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
         <x:v>Initial level marked</x:v>
       </x:c>
-      <x:c r="I3" s="39" t="str"/>
-      <x:c r="J3" s="39" t="str"/>
-      <x:c r="K3" s="39" t="str"/>
-      <x:c r="L3" s="40" t="str"/>
-      <x:c r="M3" s="41" t="str"/>
-      <x:c r="N3" s="41" t="str">
+      <x:c r="I3" s="93" t="str">
+        <x:v>No discoloration observed</x:v>
+      </x:c>
+      <x:c r="J3" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K3" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L3" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M3" s="100" t="str">
+        <x:v>day0.jpg</x:v>
+      </x:c>
+      <x:c r="N3" s="100" t="str">
         <x:v>Before exposure</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="28" t="n">
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="28" t="n">
+      <x:c r="B4" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="37" t="str"/>
-      <x:c r="D4" s="38" t="str"/>
-      <x:c r="E4" s="29" t="str">
+      <x:c r="C4" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D4" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E4" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F4" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G4" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H4" s="39" t="str">
+      <x:c r="F4" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G4" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
         <x:v>Initial level marked</x:v>
       </x:c>
-      <x:c r="I4" s="39" t="str"/>
-      <x:c r="J4" s="39" t="str"/>
-      <x:c r="K4" s="39" t="str"/>
-      <x:c r="L4" s="40" t="str"/>
-      <x:c r="M4" s="41" t="str"/>
-      <x:c r="N4" s="41" t="str">
+      <x:c r="I4" s="93" t="str">
+        <x:v>No discoloration observed</x:v>
+      </x:c>
+      <x:c r="J4" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K4" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L4" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M4" s="100" t="str">
+        <x:v>day0.jpg</x:v>
+      </x:c>
+      <x:c r="N4" s="100" t="str">
         <x:v>Before exposure</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="28" t="n">
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="n">
+      <x:c r="B5" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C5" s="37" t="str"/>
-      <x:c r="D5" s="38" t="str"/>
-      <x:c r="E5" s="29" t="str">
+      <x:c r="C5" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D5" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E5" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F5" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G5" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H5" s="39" t="str">
+      <x:c r="F5" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G5" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
         <x:v>Initial level marked</x:v>
       </x:c>
-      <x:c r="I5" s="39" t="str"/>
-      <x:c r="J5" s="39" t="str"/>
-      <x:c r="K5" s="39" t="str"/>
-      <x:c r="L5" s="40" t="str"/>
-      <x:c r="M5" s="41" t="str"/>
-      <x:c r="N5" s="41" t="str">
+      <x:c r="I5" s="93" t="str">
+        <x:v>No discoloration observed</x:v>
+      </x:c>
+      <x:c r="J5" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K5" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L5" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M5" s="100" t="str">
+        <x:v>day0.jpg</x:v>
+      </x:c>
+      <x:c r="N5" s="100" t="str">
         <x:v>Before exposure</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="28" t="n">
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="n">
+      <x:c r="B6" s="96" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C6" s="37" t="str"/>
-      <x:c r="D6" s="38" t="str"/>
-      <x:c r="E6" s="29" t="str">
+      <x:c r="C6" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D6" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E6" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F6" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G6" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H6" s="39" t="str">
+      <x:c r="F6" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G6" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
         <x:v>Initial level marked</x:v>
       </x:c>
-      <x:c r="I6" s="39" t="str"/>
-      <x:c r="J6" s="39" t="str"/>
-      <x:c r="K6" s="39" t="str"/>
-      <x:c r="L6" s="40" t="str"/>
-      <x:c r="M6" s="41" t="str"/>
-      <x:c r="N6" s="41" t="str">
+      <x:c r="I6" s="93" t="str">
+        <x:v>No discoloration observed</x:v>
+      </x:c>
+      <x:c r="J6" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K6" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L6" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M6" s="100" t="str">
+        <x:v>day0.jpg</x:v>
+      </x:c>
+      <x:c r="N6" s="100" t="str">
         <x:v>Before exposure</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="28" t="n">
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="96" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="n">
+      <x:c r="B7" s="96" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="37" t="str"/>
-      <x:c r="D7" s="38" t="str"/>
-      <x:c r="E7" s="29" t="str">
+      <x:c r="C7" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D7" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E7" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F7" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G7" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H7" s="39" t="str"/>
-      <x:c r="I7" s="39" t="str"/>
-      <x:c r="J7" s="39" t="str"/>
-      <x:c r="K7" s="39" t="str"/>
-      <x:c r="L7" s="40" t="str"/>
-      <x:c r="M7" s="41" t="str"/>
-      <x:c r="N7" s="41" t="str"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="28" t="n">
+      <x:c r="F7" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G7" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I7" s="93" t="str">
+        <x:v>No obvious change</x:v>
+      </x:c>
+      <x:c r="J7" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K7" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L7" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M7" s="100" t="str">
+        <x:v>day1.jpg</x:v>
+      </x:c>
+      <x:c r="N7" s="100" t="str">
+        <x:v>No obvious visual change reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32" customHeight="1">
+      <x:c r="A8" s="96" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B8" s="28" t="n">
+      <x:c r="B8" s="96" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="str"/>
-      <x:c r="D8" s="38" t="str"/>
-      <x:c r="E8" s="29" t="str">
+      <x:c r="C8" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D8" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E8" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F8" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G8" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H8" s="39" t="str"/>
-      <x:c r="I8" s="39" t="str"/>
-      <x:c r="J8" s="39" t="str"/>
-      <x:c r="K8" s="39" t="str"/>
-      <x:c r="L8" s="40" t="str"/>
-      <x:c r="M8" s="41" t="str"/>
-      <x:c r="N8" s="41" t="str"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="28" t="n">
+      <x:c r="F8" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G8" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I8" s="93" t="str">
+        <x:v>No obvious change</x:v>
+      </x:c>
+      <x:c r="J8" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K8" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L8" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M8" s="100" t="str">
+        <x:v>day1.jpg</x:v>
+      </x:c>
+      <x:c r="N8" s="100" t="str">
+        <x:v>No obvious visual change reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32" customHeight="1">
+      <x:c r="A9" s="96" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="n">
+      <x:c r="B9" s="96" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C9" s="37" t="str"/>
-      <x:c r="D9" s="38" t="str"/>
-      <x:c r="E9" s="29" t="str">
+      <x:c r="C9" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D9" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E9" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H9" s="39" t="str"/>
-      <x:c r="I9" s="39" t="str"/>
-      <x:c r="J9" s="39" t="str"/>
-      <x:c r="K9" s="39" t="str"/>
-      <x:c r="L9" s="40" t="str"/>
-      <x:c r="M9" s="41" t="str"/>
-      <x:c r="N9" s="41" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="28" t="n">
+      <x:c r="F9" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G9" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I9" s="93" t="str">
+        <x:v>No obvious change</x:v>
+      </x:c>
+      <x:c r="J9" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K9" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L9" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M9" s="100" t="str">
+        <x:v>day1.jpg</x:v>
+      </x:c>
+      <x:c r="N9" s="100" t="str">
+        <x:v>No obvious visual change reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32" customHeight="1">
+      <x:c r="A10" s="96" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="n">
+      <x:c r="B10" s="96" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str"/>
-      <x:c r="D10" s="38" t="str"/>
-      <x:c r="E10" s="29" t="str">
+      <x:c r="C10" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D10" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E10" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F10" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H10" s="39" t="str"/>
-      <x:c r="I10" s="39" t="str"/>
-      <x:c r="J10" s="39" t="str"/>
-      <x:c r="K10" s="39" t="str"/>
-      <x:c r="L10" s="40" t="str"/>
-      <x:c r="M10" s="41" t="str"/>
-      <x:c r="N10" s="41" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="28" t="n">
+      <x:c r="F10" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G10" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I10" s="93" t="str">
+        <x:v>No obvious change</x:v>
+      </x:c>
+      <x:c r="J10" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="K10" s="93" t="str">
+        <x:v>None observed</x:v>
+      </x:c>
+      <x:c r="L10" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M10" s="100" t="str">
+        <x:v>day1.jpg</x:v>
+      </x:c>
+      <x:c r="N10" s="100" t="str">
+        <x:v>No obvious visual change reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="32" customHeight="1">
+      <x:c r="A11" s="96" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B11" s="28" t="n">
+      <x:c r="B11" s="96" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C11" s="37" t="str"/>
-      <x:c r="D11" s="38" t="str"/>
-      <x:c r="E11" s="29" t="str">
+      <x:c r="C11" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D11" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E11" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H11" s="39" t="str"/>
-      <x:c r="I11" s="39" t="str">
+      <x:c r="F11" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G11" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I11" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J11" s="39" t="str">
+      <x:c r="J11" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K11" s="39" t="str">
+      <x:c r="K11" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="str"/>
-      <x:c r="M11" s="41" t="str"/>
-      <x:c r="N11" s="41" t="str">
+      <x:c r="L11" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M11" s="100" t="str">
+        <x:v>day2.jpg</x:v>
+      </x:c>
+      <x:c r="N11" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="28" t="n">
+    <x:row r="12" ht="32" customHeight="1">
+      <x:c r="A12" s="96" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B12" s="28" t="n">
+      <x:c r="B12" s="96" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C12" s="37" t="str"/>
-      <x:c r="D12" s="38" t="str"/>
-      <x:c r="E12" s="29" t="str">
+      <x:c r="C12" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D12" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E12" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H12" s="39" t="str"/>
-      <x:c r="I12" s="39" t="str">
+      <x:c r="F12" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G12" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I12" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="str">
+      <x:c r="J12" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="str">
+      <x:c r="K12" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L12" s="40" t="str"/>
-      <x:c r="M12" s="41" t="str"/>
-      <x:c r="N12" s="41" t="str">
+      <x:c r="L12" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M12" s="100" t="str">
+        <x:v>day2.jpg</x:v>
+      </x:c>
+      <x:c r="N12" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="28" t="n">
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="96" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="28" t="n">
+      <x:c r="B13" s="96" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C13" s="37" t="str"/>
-      <x:c r="D13" s="38" t="str"/>
-      <x:c r="E13" s="29" t="str">
+      <x:c r="C13" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D13" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E13" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F13" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H13" s="39" t="str"/>
-      <x:c r="I13" s="39" t="str">
+      <x:c r="F13" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G13" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I13" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J13" s="39" t="str">
+      <x:c r="J13" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K13" s="39" t="str">
+      <x:c r="K13" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="str"/>
-      <x:c r="M13" s="41" t="str"/>
-      <x:c r="N13" s="41" t="str">
+      <x:c r="L13" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M13" s="100" t="str">
+        <x:v>day2.jpg</x:v>
+      </x:c>
+      <x:c r="N13" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="28" t="n">
+    <x:row r="14" ht="32" customHeight="1">
+      <x:c r="A14" s="96" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B14" s="28" t="n">
+      <x:c r="B14" s="96" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C14" s="37" t="str"/>
-      <x:c r="D14" s="38" t="str"/>
-      <x:c r="E14" s="29" t="str">
+      <x:c r="C14" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D14" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E14" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F14" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G14" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H14" s="39" t="str"/>
-      <x:c r="I14" s="39" t="str">
+      <x:c r="F14" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G14" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I14" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="str">
+      <x:c r="J14" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="str">
+      <x:c r="K14" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L14" s="40" t="str"/>
-      <x:c r="M14" s="41" t="str"/>
-      <x:c r="N14" s="41" t="str">
+      <x:c r="L14" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M14" s="100" t="str">
+        <x:v>day2.jpg</x:v>
+      </x:c>
+      <x:c r="N14" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="28" t="n">
+    <x:row r="15" ht="32" customHeight="1">
+      <x:c r="A15" s="96" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B15" s="28" t="n">
+      <x:c r="B15" s="96" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C15" s="37" t="str"/>
-      <x:c r="D15" s="38" t="str"/>
-      <x:c r="E15" s="29" t="str">
+      <x:c r="C15" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D15" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E15" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F15" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G15" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H15" s="39" t="str"/>
-      <x:c r="I15" s="39" t="str">
+      <x:c r="F15" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G15" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I15" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J15" s="39" t="str">
+      <x:c r="J15" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K15" s="39" t="str">
+      <x:c r="K15" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="str"/>
-      <x:c r="M15" s="41" t="str">
-        <x:v>49e6c3a10830b5c781b08c58d3f80701(1).jpg</x:v>
-      </x:c>
-      <x:c r="N15" s="41" t="str">
+      <x:c r="L15" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M15" s="100" t="str">
+        <x:v>day3.jpg</x:v>
+      </x:c>
+      <x:c r="N15" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="28" t="n">
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="96" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B16" s="28" t="n">
+      <x:c r="B16" s="96" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C16" s="37" t="str"/>
-      <x:c r="D16" s="38" t="str"/>
-      <x:c r="E16" s="29" t="str">
+      <x:c r="C16" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D16" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E16" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F16" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G16" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H16" s="39" t="str"/>
-      <x:c r="I16" s="39" t="str">
+      <x:c r="F16" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G16" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I16" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="str">
+      <x:c r="J16" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="str">
+      <x:c r="K16" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L16" s="40" t="str"/>
-      <x:c r="M16" s="41" t="str">
-        <x:v>49e6c3a10830b5c781b08c58d3f80701(1).jpg</x:v>
-      </x:c>
-      <x:c r="N16" s="41" t="str">
+      <x:c r="L16" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M16" s="100" t="str">
+        <x:v>day3.jpg</x:v>
+      </x:c>
+      <x:c r="N16" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="28" t="n">
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="96" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B17" s="28" t="n">
+      <x:c r="B17" s="96" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C17" s="37" t="str"/>
-      <x:c r="D17" s="38" t="str"/>
-      <x:c r="E17" s="29" t="str">
+      <x:c r="C17" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D17" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E17" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F17" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H17" s="39" t="str"/>
-      <x:c r="I17" s="39" t="str">
+      <x:c r="F17" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G17" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I17" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J17" s="39" t="str">
+      <x:c r="J17" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K17" s="39" t="str">
+      <x:c r="K17" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="str"/>
-      <x:c r="M17" s="41" t="str">
-        <x:v>49e6c3a10830b5c781b08c58d3f80701(1).jpg</x:v>
-      </x:c>
-      <x:c r="N17" s="41" t="str">
+      <x:c r="L17" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M17" s="100" t="str">
+        <x:v>day3.jpg</x:v>
+      </x:c>
+      <x:c r="N17" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="28" t="n">
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="96" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B18" s="28" t="n">
+      <x:c r="B18" s="96" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C18" s="37" t="str"/>
-      <x:c r="D18" s="38" t="str"/>
-      <x:c r="E18" s="29" t="str">
+      <x:c r="C18" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D18" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E18" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F18" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H18" s="39" t="str"/>
-      <x:c r="I18" s="39" t="str">
+      <x:c r="F18" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G18" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I18" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="str">
+      <x:c r="J18" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="str">
+      <x:c r="K18" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L18" s="40" t="str"/>
-      <x:c r="M18" s="41" t="str">
-        <x:v>49e6c3a10830b5c781b08c58d3f80701(1).jpg</x:v>
-      </x:c>
-      <x:c r="N18" s="41" t="str">
+      <x:c r="L18" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M18" s="100" t="str">
+        <x:v>day3.jpg</x:v>
+      </x:c>
+      <x:c r="N18" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="28" t="n">
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="96" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="n">
+      <x:c r="B19" s="96" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C19" s="37" t="str"/>
-      <x:c r="D19" s="38" t="str"/>
-      <x:c r="E19" s="29" t="str">
+      <x:c r="C19" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D19" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E19" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F19" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G19" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H19" s="39" t="str"/>
-      <x:c r="I19" s="39" t="str">
+      <x:c r="F19" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G19" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I19" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J19" s="39" t="str">
+      <x:c r="J19" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K19" s="39" t="str">
+      <x:c r="K19" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="str"/>
-      <x:c r="M19" s="41" t="str">
-        <x:v>18be0bb039db59f0d2edf400f9dd59ba(1).jpg</x:v>
-      </x:c>
-      <x:c r="N19" s="41" t="str">
+      <x:c r="L19" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M19" s="100" t="str">
+        <x:v>day4.jpg</x:v>
+      </x:c>
+      <x:c r="N19" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="28" t="n">
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="96" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B20" s="28" t="n">
+      <x:c r="B20" s="96" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C20" s="37" t="str"/>
-      <x:c r="D20" s="38" t="str"/>
-      <x:c r="E20" s="29" t="str">
+      <x:c r="C20" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D20" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E20" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F20" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G20" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H20" s="39" t="str"/>
-      <x:c r="I20" s="39" t="str">
+      <x:c r="F20" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G20" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I20" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="str">
+      <x:c r="J20" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="str">
+      <x:c r="K20" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L20" s="40" t="str"/>
-      <x:c r="M20" s="41" t="str">
-        <x:v>18be0bb039db59f0d2edf400f9dd59ba(1).jpg</x:v>
-      </x:c>
-      <x:c r="N20" s="41" t="str">
+      <x:c r="L20" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M20" s="100" t="str">
+        <x:v>day4.jpg</x:v>
+      </x:c>
+      <x:c r="N20" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="28" t="n">
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="96" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B21" s="28" t="n">
+      <x:c r="B21" s="96" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C21" s="37" t="str"/>
-      <x:c r="D21" s="38" t="str"/>
-      <x:c r="E21" s="29" t="str">
+      <x:c r="C21" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D21" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E21" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F21" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G21" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H21" s="39" t="str"/>
-      <x:c r="I21" s="39" t="str">
+      <x:c r="F21" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G21" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I21" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J21" s="39" t="str">
+      <x:c r="J21" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K21" s="39" t="str">
+      <x:c r="K21" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="str"/>
-      <x:c r="M21" s="41" t="str">
-        <x:v>18be0bb039db59f0d2edf400f9dd59ba(1).jpg</x:v>
-      </x:c>
-      <x:c r="N21" s="41" t="str">
+      <x:c r="L21" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M21" s="100" t="str">
+        <x:v>day4.jpg</x:v>
+      </x:c>
+      <x:c r="N21" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="28" t="n">
+    <x:row r="22" ht="32" customHeight="1">
+      <x:c r="A22" s="96" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B22" s="28" t="n">
+      <x:c r="B22" s="96" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C22" s="37" t="str"/>
-      <x:c r="D22" s="38" t="str"/>
-      <x:c r="E22" s="29" t="str">
+      <x:c r="C22" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D22" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E22" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F22" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G22" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H22" s="39" t="str"/>
-      <x:c r="I22" s="39" t="str">
+      <x:c r="F22" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G22" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I22" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="str">
+      <x:c r="J22" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="str">
+      <x:c r="K22" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L22" s="40" t="str"/>
-      <x:c r="M22" s="41" t="str">
-        <x:v>18be0bb039db59f0d2edf400f9dd59ba(1).jpg</x:v>
-      </x:c>
-      <x:c r="N22" s="41" t="str">
+      <x:c r="L22" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M22" s="100" t="str">
+        <x:v>day4.jpg</x:v>
+      </x:c>
+      <x:c r="N22" s="100" t="str">
         <x:v>No obvious visual change reported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="28" t="n">
+    <x:row r="23" ht="32" customHeight="1">
+      <x:c r="A23" s="96" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B23" s="28" t="n">
+      <x:c r="B23" s="96" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C23" s="37" t="str"/>
-      <x:c r="D23" s="38" t="str"/>
-      <x:c r="E23" s="29" t="str">
+      <x:c r="C23" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D23" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E23" s="94" t="str">
         <x:v>S1</x:v>
       </x:c>
-      <x:c r="F23" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H23" s="39" t="str"/>
-      <x:c r="I23" s="39" t="str">
+      <x:c r="F23" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G23" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I23" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J23" s="39" t="str">
+      <x:c r="J23" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K23" s="39" t="str">
+      <x:c r="K23" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="str"/>
-      <x:c r="M23" s="41" t="str">
-        <x:v>35a749ee21f06c9076b2076148091a84(1).jpg</x:v>
-      </x:c>
-      <x:c r="N23" s="41" t="str">
+      <x:c r="L23" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M23" s="100" t="str">
+        <x:v>day5.jpg</x:v>
+      </x:c>
+      <x:c r="N23" s="100" t="str">
         <x:v>No obvious macroscopic change in liquid clarity, deposits, or electrode appearance at the 120-hour endpoint.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="28" t="n">
+    <x:row r="24" ht="32" customHeight="1">
+      <x:c r="A24" s="96" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="28" t="n">
+      <x:c r="B24" s="96" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C24" s="37" t="str"/>
-      <x:c r="D24" s="38" t="str"/>
-      <x:c r="E24" s="29" t="str">
+      <x:c r="C24" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D24" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E24" s="94" t="str">
         <x:v>S2</x:v>
       </x:c>
-      <x:c r="F24" s="29" t="str">
-        <x:v>Saline exposure</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="str">
-        <x:v>3.5% NaCl solution</x:v>
-      </x:c>
-      <x:c r="H24" s="39" t="str"/>
-      <x:c r="I24" s="39" t="str">
+      <x:c r="F24" s="94" t="str">
+        <x:v>Saline exposure</x:v>
+      </x:c>
+      <x:c r="G24" s="94" t="str">
+        <x:v>3.5% NaCl solution</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I24" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="str">
+      <x:c r="J24" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="str">
+      <x:c r="K24" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L24" s="40" t="str"/>
-      <x:c r="M24" s="41" t="str">
-        <x:v>35a749ee21f06c9076b2076148091a84(1).jpg</x:v>
-      </x:c>
-      <x:c r="N24" s="41" t="str">
+      <x:c r="L24" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M24" s="100" t="str">
+        <x:v>day5.jpg</x:v>
+      </x:c>
+      <x:c r="N24" s="100" t="str">
         <x:v>No obvious macroscopic change in liquid clarity, deposits, or electrode appearance at the 120-hour endpoint.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="28" t="n">
+    <x:row r="25" ht="32" customHeight="1">
+      <x:c r="A25" s="96" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B25" s="28" t="n">
+      <x:c r="B25" s="96" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C25" s="37" t="str"/>
-      <x:c r="D25" s="38" t="str"/>
-      <x:c r="E25" s="29" t="str">
+      <x:c r="C25" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D25" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E25" s="94" t="str">
         <x:v>C1</x:v>
       </x:c>
-      <x:c r="F25" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G25" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H25" s="39" t="str"/>
-      <x:c r="I25" s="39" t="str">
+      <x:c r="F25" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G25" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I25" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J25" s="39" t="str">
+      <x:c r="J25" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K25" s="39" t="str">
+      <x:c r="K25" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="str"/>
-      <x:c r="M25" s="41" t="str">
-        <x:v>35a749ee21f06c9076b2076148091a84(1).jpg</x:v>
-      </x:c>
-      <x:c r="N25" s="41" t="str">
+      <x:c r="L25" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M25" s="100" t="str">
+        <x:v>day5.jpg</x:v>
+      </x:c>
+      <x:c r="N25" s="100" t="str">
         <x:v>No obvious macroscopic change in liquid clarity, deposits, or electrode appearance at the 120-hour endpoint.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="28" t="n">
+    <x:row r="26" ht="32" customHeight="1">
+      <x:c r="A26" s="96" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B26" s="28" t="n">
+      <x:c r="B26" s="96" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C26" s="37" t="str"/>
-      <x:c r="D26" s="38" t="str"/>
-      <x:c r="E26" s="29" t="str">
+      <x:c r="C26" s="97" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="D26" s="98" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="E26" s="94" t="str">
         <x:v>C2</x:v>
       </x:c>
-      <x:c r="F26" s="29" t="str">
-        <x:v>Water control</x:v>
-      </x:c>
-      <x:c r="G26" s="29" t="str">
-        <x:v>Ordinary water</x:v>
-      </x:c>
-      <x:c r="H26" s="39" t="str"/>
-      <x:c r="I26" s="39" t="str">
+      <x:c r="F26" s="94" t="str">
+        <x:v>Water control</x:v>
+      </x:c>
+      <x:c r="G26" s="94" t="str">
+        <x:v>Ordinary water</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="I26" s="93" t="str">
         <x:v>No obvious change</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="str">
+      <x:c r="J26" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="str">
+      <x:c r="K26" s="93" t="str">
         <x:v>None observed</x:v>
       </x:c>
-      <x:c r="L26" s="40" t="str"/>
-      <x:c r="M26" s="41" t="str">
-        <x:v>35a749ee21f06c9076b2076148091a84(1).jpg</x:v>
-      </x:c>
-      <x:c r="N26" s="41" t="str">
+      <x:c r="L26" s="99" t="str">
+        <x:v>Not recorded</x:v>
+      </x:c>
+      <x:c r="M26" s="100" t="str">
+        <x:v>day5.jpg</x:v>
+      </x:c>
+      <x:c r="N26" s="100" t="str">
         <x:v>No obvious macroscopic change in liquid clarity, deposits, or electrode appearance at the 120-hour endpoint.</x:v>
       </x:c>
     </x:row>
@@ -4115,7 +4394,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc741cfef506c43f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9a80fa4f91a4819"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5823,7 +6102,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc60c31255a3f4ce2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R969a5c153ae04149"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6352,7 +6631,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc537b8aaf3048e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fb561a5003a4281"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6545,7 +6824,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b79f07b007f4101"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a3eb001bef44c69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7017,6 +7296,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71c9637628a4059"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a75945d18242f5"/>
 </x:worksheet>
 </file>